--- a/Assets/Document/云熹约定项目文档/9.特殊剧情配置表/周杉/xlsx/周杉事件五.xlsx
+++ b/Assets/Document/云熹约定项目文档/9.特殊剧情配置表/周杉/xlsx/周杉事件五.xlsx
@@ -1,179 +1,892 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="230">
+  <si>
+    <t>角色编号</t>
+  </si>
+  <si>
+    <t>台词编号</t>
+  </si>
+  <si>
+    <t>台词 / 旁白文本</t>
+  </si>
+  <si>
+    <t>立绘 / 动作提示</t>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>周六上午十点，游乐园门口人声鼎沸</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>早晨的阳光明媚得有些晃眼，你眯着眼睛看了一眼天空，万里无云，是个好天气</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>你拎着装着拍摄设备的托特包，沉甸甸的，单肩背着有点勒</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>你走到约定的喷泉广场，视线在人群中扫了一圈</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>然后，你的视线自动锁定了一个挺拔的身影，那是一个穿着干净白 T 恤和浅色水洗牛仔裤的年轻男生</t>
+  </si>
+  <si>
+    <t>0000</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>他正低头看着手机里的地图导航，手指在屏幕上划来划去，像是在确认路线</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>或许是坐了几个小时的大巴，他的眉宇间带着一丝不易察觉的倦色</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>眼底有一层淡淡的青黑，嘴唇的颜色也比正常人淡一些，但他的脊背却挺得笔直</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>似乎是察觉到了你的注视，他抬起头</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>那双清澈的眼眸在人群中精准地捕捉到了你，就像是在一个满是噪点的画面里，突然锁定了焦点</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>原本因为疲惫而微微抿起的唇角，瞬间扬起了一个温和却克制的弧度</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>“老板，这里。”</t>
+  </si>
+  <si>
+    <t>013</t>
+  </si>
+  <si>
+    <t>他快步走到你面前，脚步很快，但不会让你觉得急躁</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>那是一个等了很久的人，终于等到的时候，不自觉地加快的步频</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>他自然地伸出手，接过了你手里沉甸甸的设备包，动作妥帖得仿佛你们已经认识了很久</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>“初次见面，我是周杉，也是…… 你的时安。”</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>他说 “你的时安” 的时候，声音轻了一点。像是犹豫了一下要不要加上 “你的”，但最终还是说了</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>他的声音在现实中听起来比隔着网线时少了几分刻意打磨的失真感，多了一丝属于年轻人的清朗</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>这种阳光的外表，与你脑海中那个深夜里成熟克制的嗓音，形成了极具张力的反差</t>
+  </si>
+  <si>
+    <t>020</t>
+  </si>
+  <si>
+    <t>你突然明白了一件事，他在网上的那种成熟，不是天生的，是练出来的</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>是在无数个深夜里，对着屏幕，一个字一个字地调整语气、控制情绪、把自己打磨成别人想要的样子</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
+    <t>而此刻站在你面前的这个人，才是真正的他</t>
+  </si>
+  <si>
+    <t>023</t>
+  </si>
+  <si>
+    <t>这一天，他如约履行了苦力的职责，展现出了极高的社交素养和观察力</t>
+  </si>
+  <si>
+    <t>024</t>
+  </si>
+  <si>
+    <t>不仅熟练地为你开路，在人群中侧着身子帮你挡住拥挤的人流；还能在你举起相机时，默契地举起反光板，角度调整得刚刚好</t>
+  </si>
+  <si>
+    <t>025</t>
+  </si>
+  <si>
+    <t>他甚至会在你还没开口的时候，就提前买好饮料，拧开盖子，递到你面前</t>
+  </si>
+  <si>
+    <t>026</t>
+  </si>
+  <si>
+    <t>但他不再是那个情绪稳定的完美陪玩，当过山车猛地俯冲时，你会看到他下意识握紧安全压杆，嘴抿成一条直线</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
+    <t>但他没有叫出来，只是等那一阵失重感过去，对你笑着说 “有点刺激”</t>
+  </si>
+  <si>
+    <t>028</t>
+  </si>
+  <si>
+    <t>当他吃到网红摊位上味道不错的海盐冰淇淋时，眼底会流露出真实的满足感</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>这种充满生命力的鲜活感，让习惯了做观察者的你，也不自觉地卸下了防备</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
+    <t>你发现，和他呆在一起的时候，你不需要想太多</t>
+  </si>
+  <si>
+    <t>031</t>
+  </si>
+  <si>
+    <t>他会在你犹豫的时候给出建议，在你累了的时候找到长椅，在你举起相机的时候默默退到一边</t>
+  </si>
+  <si>
+    <t>032</t>
+  </si>
+  <si>
+    <t>他不会问 “你在拍什么”“为什么要拍这个”，他只是给你空间，让你做你想做的事</t>
+  </si>
+  <si>
+    <t>033</t>
+  </si>
+  <si>
+    <t>这是一种很奇怪的默契，你们认识的时间不长，但相处起来，像是已经磨合了很久</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>夕阳落下时，素材已经录制得差不多了</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>作为游玩的最后一站，你们坐上了游乐园的摩天轮</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t>轿厢不大，两个人面对面坐着，膝盖几乎要碰到一起</t>
+  </si>
+  <si>
+    <t>037</t>
+  </si>
+  <si>
+    <t>随着轿厢缓缓升空，游乐园的喧嚣被渐渐远离</t>
+  </si>
+  <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>那些尖叫声、音乐声、广播声，都变成了模糊的背景音，越来越远，越来越轻</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>夕阳的余晖透过玻璃洒进轿厢，为他的侧脸镀上了一层温柔而深邃的金边</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>他的睫毛很长，在脸颊上投下一小片阴影。他看着窗外逐渐缩小的建筑，神情很安静，安静得让你觉得他此刻在想很多事</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>他转过头看着你，眼里倒映着细碎的光</t>
+  </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t>“其实从小到大，都没人带我来过游乐园。”</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>这是一个引子，你看着他，静静地听</t>
+  </si>
+  <si>
+    <t>044</t>
+  </si>
+  <si>
+    <t>他讲了很多他的过去，像是要把自己完全展示给你看</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>他的眼里不再有雇佣关系的讨好，只有成年人之间率真且坦诚的直白，他微微倾身</t>
+  </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>距离拉近的时候，你能闻到他身上那股干净的、属于秋日草木的清冽气息</t>
+  </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>“我知道你很成熟、很强大，不需要依赖任何人。我没资格说保护你这种不自量力的大话……”</t>
+  </si>
+  <si>
+    <t>048</t>
+  </si>
+  <si>
+    <t>他的声音放得很慢，像是在斟酌每一个字的分量</t>
+  </si>
+  <si>
+    <t>049</t>
+  </si>
+  <si>
+    <t>“但是，我想试着跨出那条边界。我想成为你在这个世界上，可以偶尔卸下防备的、能随时依靠的底牌。”</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>摩天轮升到了最高点，整个城市的轮廓在你脚下展开，夕阳把一切都染成了金红色</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>你看着他，他的眼睛里倒映着夕阳的光，还有你的影子</t>
+  </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
+    <t>【抉择选项】拒绝，止步友情</t>
+  </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>他还是把藏在心底的话说出来了，对此你并不感到意外</t>
+  </si>
+  <si>
+    <t>054</t>
+  </si>
+  <si>
+    <t>他的表情很认真，认真到你能看见他下颌线因为紧张而微微发紧</t>
+  </si>
+  <si>
+    <t>055</t>
+  </si>
+  <si>
+    <t>但你并不觉得那是可以被称为 “喜欢” 的感情，他对你或许只是一种依赖，而这种依赖在见到你之后落到了实处</t>
+  </si>
+  <si>
+    <t>056</t>
+  </si>
+  <si>
+    <t>虽然被他的真诚打动，但理智依然牢牢占据着上风</t>
+  </si>
+  <si>
+    <t>057</t>
+  </si>
+  <si>
+    <t>虚拟的陪伴很完美，但现实的羁绊太沉重，更何况现实中还有诸多要考虑的因素</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>058</t>
+  </si>
+  <si>
+    <t>“你还年轻，可能是刺激项目带来的吊桥效应，让你错把乱了拍子的心跳当成了心动。”</t>
+  </si>
+  <si>
+    <t>059</t>
+  </si>
+  <si>
+    <t>你故意用了吊桥效应这个词，一个心理学名词，足够冷静理性，足够把这段对话拉回到分析的层面</t>
+  </si>
+  <si>
+    <t>060</t>
+  </si>
+  <si>
+    <t>“虚拟和现实是两回事，我们还是做朋友吧。”</t>
+  </si>
+  <si>
+    <t>061</t>
+  </si>
+  <si>
+    <t>说到朋友二字的时候，你特意把重音放在了后面，这是你能给的最大限度</t>
+  </si>
+  <si>
+    <t>062</t>
+  </si>
+  <si>
+    <t>他的眼睛暗了一下，像是一盏灯被轻轻关上。他垂下眼眸，睫毛在脸颊上投下一片阴影</t>
+  </si>
+  <si>
+    <t>063</t>
+  </si>
+  <si>
+    <t>他沉默了几秒，然后他抬起头，对你笑了笑</t>
+  </si>
+  <si>
+    <t>064</t>
+  </si>
+  <si>
+    <t>那个笑容里没有委屈，没有不甘，只有一种克制的、不想让你为难的温柔</t>
+  </si>
+  <si>
+    <t>065</t>
+  </si>
+  <si>
+    <t>“对不起，是我冒昧了。既然是你的决定，我接受。能以朋友的身份陪着你，我已经很知足了。”</t>
+  </si>
+  <si>
+    <t>066</t>
+  </si>
+  <si>
+    <t>摩天轮开始下降。城市的轮廓从眼前慢慢滑过，夕阳的光线变成了更深的橘红色</t>
+  </si>
+  <si>
+    <t>067</t>
+  </si>
+  <si>
+    <t>他站起来，帮你拿起设备包，动作还是那么妥帖，还是那么自然</t>
+  </si>
+  <si>
+    <t>068</t>
+  </si>
+  <si>
+    <t>“天黑了，你回家路上千万当心。”</t>
+  </si>
+  <si>
+    <t>069</t>
+  </si>
+  <si>
+    <t>你们在游乐园门口分道扬镳，夜风带着一丝凉意掠过，吹起你的头发</t>
+  </si>
+  <si>
+    <t>070</t>
+  </si>
+  <si>
+    <t>你回头看了一眼，他站在原地，安静地望着你的背影</t>
+  </si>
+  <si>
+    <t>071</t>
+  </si>
+  <si>
+    <t>没有追上来。没有再多说一句打扰的话</t>
+  </si>
+  <si>
+    <t>072</t>
+  </si>
+  <si>
+    <t>那份被你推开的心意，他妥帖收好，没有半分怨怼，只剩无声的体谅</t>
+  </si>
+  <si>
+    <t>073</t>
+  </si>
+  <si>
+    <t>你转过身，继续往前走</t>
+  </si>
+  <si>
+    <t>074</t>
+  </si>
+  <si>
+    <t>你压下心底片刻的酸涩，那酸涩来得莫名其妙，你甚至分不清是什么情感</t>
+  </si>
+  <si>
+    <t>075</t>
+  </si>
+  <si>
+    <t>但你更清楚，理智的拒绝才是对两个人最负责的答案</t>
+  </si>
+  <si>
+    <t>076</t>
+  </si>
+  <si>
+    <t>有些心动适合停留在屏幕那头，有些陪伴，止步于朋友才最长久</t>
+  </si>
+  <si>
+    <t>077</t>
+  </si>
+  <si>
+    <t>【抉择选项】接受，关系升华</t>
+  </si>
+  <si>
+    <t>078</t>
+  </si>
+  <si>
+    <t>你看着他因为紧张而微微发紧的下颌线，以及那双执着专注的眼睛</t>
+  </si>
+  <si>
+    <t>079</t>
+  </si>
+  <si>
+    <t>他对你的情感很微妙特别，你们的接触不多不少，没有夸张到一见钟情，也没有长久到细水长流</t>
+  </si>
+  <si>
+    <t>080</t>
+  </si>
+  <si>
+    <t>但是相处时的舒适合拍，确实也让你重新审视起你们之间的关系，你似乎也并不排斥生活中多一个合拍的搭档</t>
+  </si>
+  <si>
+    <t>081</t>
+  </si>
+  <si>
+    <t>面对这份赤诚直白，你决定允许自己感性一次</t>
+  </si>
+  <si>
+    <t>082</t>
+  </si>
+  <si>
+    <t>“想要成为我的底牌，门槛可是很高的。”</t>
+  </si>
+  <si>
+    <t>083</t>
+  </si>
+  <si>
+    <t>你故意停顿了一下，语气拖长</t>
+  </si>
+  <si>
+    <t>084</t>
+  </si>
+  <si>
+    <t>肉眼可见地，那双原本充满希冀的清澈眼眸，因为你这句看似拒绝的话，瞬间黯淡了</t>
+  </si>
+  <si>
+    <t>085</t>
+  </si>
+  <si>
+    <t>他的瞳孔微微收缩，连脊背都微微僵硬，像是一棵被风吹弯了的树，在等一个宣判</t>
+  </si>
+  <si>
+    <t>086</t>
+  </si>
+  <si>
+    <t>看到他的沮丧，你才把后半句说完</t>
+  </si>
+  <si>
+    <t>087</t>
+  </si>
+  <si>
+    <t>“但…… 试试看吧，看看真实的你，能不能接得住我。”</t>
+  </si>
+  <si>
+    <t>088</t>
+  </si>
+  <si>
+    <t>话音刚落，他的眼底瞬间绽放出难以置信的光芒</t>
+  </si>
+  <si>
+    <t>089</t>
+  </si>
+  <si>
+    <t>那光芒太亮了，亮得盖住了夕阳</t>
+  </si>
+  <si>
+    <t>090</t>
+  </si>
+  <si>
+    <t>他张了张嘴，像是想说什么，但喉咙像是被什么堵住，他的呼吸停滞了一瞬，你看见他的胸口起伏了一下，然后停住了</t>
+  </si>
+  <si>
+    <t>091</t>
+  </si>
+  <si>
+    <t>他没有做出任何逾矩的动作，没有扑过来，没有激动地抓住你的手</t>
+  </si>
+  <si>
+    <t>092</t>
+  </si>
+  <si>
+    <t>他只是极其郑重地伸出手，将你轻轻拥入怀中</t>
+  </si>
+  <si>
+    <t>093</t>
+  </si>
+  <si>
+    <t>那个拥抱很轻，轻到你能感觉到他在控制自己的力道。他浑身都在发抖，但他的手臂只是松松地环着你，像捧着一件易碎品</t>
+  </si>
+  <si>
+    <t>094</t>
+  </si>
+  <si>
+    <t>不带任何情欲，却充满了一种令人心悸的坚定</t>
+  </si>
+  <si>
+    <t>095</t>
+  </si>
+  <si>
+    <t>然后他的声音从你头顶传来，沙哑的，带着一丝颤抖</t>
+  </si>
+  <si>
+    <t>096</t>
+  </si>
+  <si>
+    <t>“谢谢……谢谢。”</t>
+  </si>
+  <si>
+    <t>097</t>
+  </si>
+  <si>
+    <t>他只说了这两个字，但这两个字里，藏了他过去二十三年所有的委屈、孤独和不被看见</t>
+  </si>
+  <si>
+    <t>098</t>
+  </si>
+  <si>
+    <t>摩天轮开始下降，城市的灯光一盏一盏地亮起来，像地上的星星</t>
+  </si>
+  <si>
+    <t>099</t>
+  </si>
+  <si>
+    <t>他松开你的时候，耳尖红了一片。他别过头，假装看窗外的风景，但玻璃上倒映出的他的脸，嘴角是弯着的</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>从摩天轮上下来的时候天已经擦黑，时间不早了，你催促他早些回学校</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>他却执意要把你先送回家，美其名曰太晚了一个人不安全</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>你哭笑不得，这么多年来你一直如此，但如今不再是一个人，也就没有拂了他的意</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>电梯门关上的那一刻，你的手机震了一下。你低头一看，是他的消息</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>“今天是我这辈子最开心的一天。”</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>你盯着那行字看了几秒，然后随手回了几个字</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>“明天会更开心。”</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>发出去之后，你觉得自己好像说了什么了不得的话，想撤回但已经来不及了</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>“那我可以期待一下明天吗？”</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>“嗯。”</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>你把手机息屏放进口袋，窗外城市的灯火一盏一盏地亮着</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>你靠着窗，看着远处的霓虹，觉得今晚的夜色，格外温柔</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="20">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -473,156 +1186,159 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -678,74 +1394,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -997,43 +1650,1333 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D112"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="115" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>